--- a/artfynd/A 61583-2025 artfynd.xlsx
+++ b/artfynd/A 61583-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>129688666</v>
       </c>
       <c r="B5" t="n">
-        <v>79183</v>
+        <v>79184</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>129688242</v>
       </c>
       <c r="B6" t="n">
-        <v>97675</v>
+        <v>97692</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129688667</v>
       </c>
       <c r="B7" t="n">
-        <v>97675</v>
+        <v>97692</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
